--- a/results/reliability_eval/Llama-3-8B_P176_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P176_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4532321973266855</v>
+        <v>0.7024815108195945</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8697079754281263</v>
+        <v>0.9161926257103677</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4532321973266855</v>
+        <v>0.7024815108195945</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8697079754281263</v>
+        <v>0.916194544899381</v>
       </c>
       <c r="E2" t="n">
-        <v>0.545658144083341</v>
+        <v>0.2915664166894928</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8784760881577152</v>
+        <v>0.7688827369826142</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9994477041721136</v>
+        <v>0.9985601018663153</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998778663902967</v>
+        <v>0.9996427347833242</v>
       </c>
       <c r="I2" t="n">
-        <v>0.889</v>
+        <v>0.839</v>
       </c>
     </row>
   </sheetData>
